--- a/jutyu_linkmaster.xlsx
+++ b/jutyu_linkmaster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\The-portal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87D87B7C-5C63-4A2F-8408-159080AC617D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6E5874-2414-4D90-BA9D-A388A39F3E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2430" windowWidth="29040" windowHeight="15720" xr2:uid="{374FBEBE-E52A-4E12-875E-174B8688DDA0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{374FBEBE-E52A-4E12-875E-174B8688DDA0}"/>
   </bookViews>
   <sheets>
     <sheet name="パスワード一覧" sheetId="1" r:id="rId1"/>
@@ -1395,13 +1395,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFBDBDBD"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FFBDBDBD"/>
         </left>
@@ -1411,6 +1404,13 @@
         <top style="thin">
           <color rgb="FFBDBDBD"/>
         </top>
+        <bottom style="thin">
+          <color rgb="FFBDBDBD"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FFBDBDBD"/>
         </bottom>
@@ -1493,7 +1493,7 @@
                   <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBA685D5-D69F-47F7-9BCE-FE14D4FDE915}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1569,7 +1569,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0826CE99-8988-445F-A696-1F51AE1AEBA2}" name="テーブル1" displayName="テーブル1" ref="A1:E24" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5" headerRowCellStyle="標準 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0826CE99-8988-445F-A696-1F51AE1AEBA2}" name="テーブル1" displayName="テーブル1" ref="A1:E24" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5" headerRowCellStyle="標準 2">
   <autoFilter ref="A1:E24" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1B365226-3106-4815-84B4-F39B5EDE6A78}" name="サービス名（わかりやすい名前）" dataDxfId="4" dataCellStyle="標準 2"/>
